--- a/2025/BELTRAN 34/Libro1.xlsx
+++ b/2025/BELTRAN 34/Libro1.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\BELTRAN 34\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2025\BELTRAN 34\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D6BA27E-B863-4C97-B583-5F690A64921F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50904A39-403D-474E-8965-62CEE6B7710F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{40F7CB68-AA62-4B90-B02B-2F8168283C84}"/>
   </bookViews>
@@ -135,17 +135,11 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -156,7 +150,13 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -485,28 +485,28 @@
   </cols>
   <sheetData>
     <row r="4" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E4" s="11" t="s">
+      <c r="E4" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="F4" s="11"/>
-      <c r="G4" s="11"/>
-      <c r="H4" s="11"/>
-      <c r="I4" s="11"/>
-      <c r="J4" s="11"/>
-      <c r="K4" s="11"/>
+      <c r="F4" s="9"/>
+      <c r="G4" s="9"/>
+      <c r="H4" s="9"/>
+      <c r="I4" s="9"/>
+      <c r="J4" s="9"/>
+      <c r="K4" s="9"/>
     </row>
     <row r="6" spans="5:11" x14ac:dyDescent="0.3">
       <c r="E6" t="s">
         <v>1</v>
       </c>
-      <c r="F6" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I6" s="5"/>
+      <c r="F6" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G6" s="6"/>
+      <c r="H6" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I6" s="6"/>
       <c r="K6" t="s">
         <v>4</v>
       </c>
@@ -515,14 +515,14 @@
       <c r="E7" s="1">
         <v>45658</v>
       </c>
-      <c r="F7" s="7">
+      <c r="F7" s="12">
         <v>43440</v>
       </c>
-      <c r="G7" s="7"/>
-      <c r="H7" s="7">
+      <c r="G7" s="12"/>
+      <c r="H7" s="12">
         <v>23892</v>
       </c>
-      <c r="I7" s="7"/>
+      <c r="I7" s="12"/>
       <c r="K7" s="3">
         <f>(F7+H7)*3%</f>
         <v>2019.96</v>
@@ -532,14 +532,14 @@
       <c r="E10" t="s">
         <v>1</v>
       </c>
-      <c r="F10" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G10" s="5"/>
-      <c r="H10" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I10" s="5"/>
+      <c r="F10" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G10" s="6"/>
+      <c r="H10" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I10" s="6"/>
       <c r="K10" t="s">
         <v>4</v>
       </c>
@@ -549,14 +549,14 @@
         <f>E7+31</f>
         <v>45689</v>
       </c>
-      <c r="F11" s="7">
+      <c r="F11" s="12">
         <v>54300</v>
       </c>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7">
+      <c r="G11" s="12"/>
+      <c r="H11" s="12">
         <v>23892</v>
       </c>
-      <c r="I11" s="7"/>
+      <c r="I11" s="12"/>
       <c r="K11" s="3">
         <f>(F11+H11)*3%</f>
         <v>2345.7599999999998</v>
@@ -566,14 +566,14 @@
       <c r="E14" t="s">
         <v>1</v>
       </c>
-      <c r="F14" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G14" s="5"/>
-      <c r="H14" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I14" s="5"/>
+      <c r="F14" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G14" s="6"/>
+      <c r="H14" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I14" s="6"/>
       <c r="K14" t="s">
         <v>4</v>
       </c>
@@ -583,14 +583,14 @@
         <f>E11+31</f>
         <v>45720</v>
       </c>
-      <c r="F15" s="7">
+      <c r="F15" s="12">
         <v>70590</v>
       </c>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7">
+      <c r="G15" s="12"/>
+      <c r="H15" s="12">
         <v>23892</v>
       </c>
-      <c r="I15" s="7"/>
+      <c r="I15" s="12"/>
       <c r="K15" s="3">
         <f>(F15+H15)*3%</f>
         <v>2834.46</v>
@@ -600,14 +600,14 @@
       <c r="E18" t="s">
         <v>1</v>
       </c>
-      <c r="F18" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G18" s="5"/>
-      <c r="H18" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I18" s="5"/>
+      <c r="F18" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="H18" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I18" s="6"/>
       <c r="K18" t="s">
         <v>4</v>
       </c>
@@ -617,12 +617,12 @@
         <f>E15+31</f>
         <v>45751</v>
       </c>
-      <c r="F19" s="7">
+      <c r="F19" s="12">
         <v>86880</v>
       </c>
-      <c r="G19" s="7"/>
-      <c r="H19" s="5"/>
-      <c r="I19" s="5"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="6"/>
+      <c r="I19" s="6"/>
       <c r="K19" s="3">
         <f>(F19+H19)*3%</f>
         <v>2606.4</v>
@@ -632,14 +632,14 @@
       <c r="E22" t="s">
         <v>1</v>
       </c>
-      <c r="F22" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G22" s="5"/>
-      <c r="H22" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I22" s="5"/>
+      <c r="F22" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G22" s="6"/>
+      <c r="H22" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I22" s="6"/>
       <c r="K22" t="s">
         <v>4</v>
       </c>
@@ -649,12 +649,12 @@
         <f>E19+31</f>
         <v>45782</v>
       </c>
-      <c r="F23" s="7">
+      <c r="F23" s="12">
         <v>86880</v>
       </c>
-      <c r="G23" s="7"/>
-      <c r="H23" s="5"/>
-      <c r="I23" s="5"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="6"/>
+      <c r="I23" s="6"/>
       <c r="K23" s="3">
         <f>(F23+H23)*3%</f>
         <v>2606.4</v>
@@ -664,14 +664,14 @@
       <c r="E26" t="s">
         <v>1</v>
       </c>
-      <c r="F26" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G26" s="6"/>
-      <c r="H26" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I26" s="6"/>
+      <c r="F26" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G26" s="10"/>
+      <c r="H26" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I26" s="10"/>
       <c r="K26" t="s">
         <v>4</v>
       </c>
@@ -681,12 +681,12 @@
         <f>E23+31</f>
         <v>45813</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="11">
         <v>97740</v>
       </c>
-      <c r="G27" s="12"/>
-      <c r="H27" s="6"/>
-      <c r="I27" s="6"/>
+      <c r="G27" s="11"/>
+      <c r="H27" s="10"/>
+      <c r="I27" s="10"/>
       <c r="K27" s="3">
         <f>(F27+H27)*3%</f>
         <v>2932.2</v>
@@ -696,14 +696,14 @@
       <c r="E30" t="s">
         <v>1</v>
       </c>
-      <c r="F30" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G30" s="5"/>
-      <c r="H30" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I30" s="5"/>
+      <c r="F30" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G30" s="6"/>
+      <c r="H30" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="6"/>
       <c r="K30" t="s">
         <v>4</v>
       </c>
@@ -713,12 +713,12 @@
         <f>E27+31</f>
         <v>45844</v>
       </c>
-      <c r="F31" s="7">
+      <c r="F31" s="12">
         <v>55903.81</v>
       </c>
-      <c r="G31" s="7"/>
-      <c r="H31" s="5"/>
-      <c r="I31" s="5"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="6"/>
+      <c r="I31" s="6"/>
       <c r="K31" s="3">
         <f>(F31+H31)*3%</f>
         <v>1677.1143</v>
@@ -734,14 +734,14 @@
       <c r="E34" t="s">
         <v>1</v>
       </c>
-      <c r="F34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G34" s="6"/>
-      <c r="H34" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I34" s="6"/>
+      <c r="F34" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G34" s="10"/>
+      <c r="H34" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I34" s="10"/>
       <c r="K34" t="s">
         <v>4</v>
       </c>
@@ -751,12 +751,12 @@
         <f>E31+31</f>
         <v>45875</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="11">
         <v>124890</v>
       </c>
-      <c r="G35" s="12"/>
-      <c r="H35" s="6"/>
-      <c r="I35" s="6"/>
+      <c r="G35" s="11"/>
+      <c r="H35" s="10"/>
+      <c r="I35" s="10"/>
       <c r="K35" s="3">
         <f>(F35+H35)*3%</f>
         <v>3746.7</v>
@@ -766,14 +766,14 @@
       <c r="E38" t="s">
         <v>1</v>
       </c>
-      <c r="F38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="G38" s="6"/>
-      <c r="H38" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="I38" s="6"/>
+      <c r="F38" s="10" t="s">
+        <v>2</v>
+      </c>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10" t="s">
+        <v>3</v>
+      </c>
+      <c r="I38" s="10"/>
       <c r="K38" t="s">
         <v>4</v>
       </c>
@@ -783,10 +783,10 @@
         <f>E35+31</f>
         <v>45906</v>
       </c>
-      <c r="F39" s="12"/>
-      <c r="G39" s="12"/>
-      <c r="H39" s="6"/>
-      <c r="I39" s="6"/>
+      <c r="F39" s="11"/>
+      <c r="G39" s="11"/>
+      <c r="H39" s="10"/>
+      <c r="I39" s="10"/>
       <c r="K39" s="3">
         <f>(F39+H39)*3%</f>
         <v>0</v>
@@ -796,14 +796,14 @@
       <c r="E42" t="s">
         <v>1</v>
       </c>
-      <c r="F42" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G42" s="5"/>
-      <c r="H42" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I42" s="5"/>
+      <c r="F42" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G42" s="6"/>
+      <c r="H42" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I42" s="6"/>
       <c r="K42" t="s">
         <v>4</v>
       </c>
@@ -813,12 +813,12 @@
         <f>E39+31</f>
         <v>45937</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="12">
         <v>106428</v>
       </c>
-      <c r="G43" s="7"/>
-      <c r="H43" s="5"/>
-      <c r="I43" s="5"/>
+      <c r="G43" s="12"/>
+      <c r="H43" s="6"/>
+      <c r="I43" s="6"/>
       <c r="K43" s="3">
         <f>(F43+H43)*3%</f>
         <v>3192.8399999999997</v>
@@ -828,14 +828,14 @@
       <c r="E46" t="s">
         <v>1</v>
       </c>
-      <c r="F46" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G46" s="5"/>
-      <c r="H46" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I46" s="5"/>
+      <c r="F46" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G46" s="6"/>
+      <c r="H46" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I46" s="6"/>
       <c r="K46" t="s">
         <v>4</v>
       </c>
@@ -845,12 +845,12 @@
         <f>E43+31</f>
         <v>45968</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="12">
         <v>157470</v>
       </c>
-      <c r="G47" s="7"/>
-      <c r="H47" s="5"/>
-      <c r="I47" s="5"/>
+      <c r="G47" s="12"/>
+      <c r="H47" s="6"/>
+      <c r="I47" s="6"/>
       <c r="K47" s="3">
         <f>(F47+H47)*3%</f>
         <v>4724.0999999999995</v>
@@ -860,14 +860,14 @@
       <c r="E50" t="s">
         <v>1</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="G50" s="5"/>
-      <c r="H50" s="5" t="s">
-        <v>3</v>
-      </c>
-      <c r="I50" s="5"/>
+      <c r="F50" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="G50" s="6"/>
+      <c r="H50" s="6" t="s">
+        <v>3</v>
+      </c>
+      <c r="I50" s="6"/>
       <c r="K50" t="s">
         <v>4</v>
       </c>
@@ -877,13 +877,15 @@
         <f>E47+31</f>
         <v>45999</v>
       </c>
-      <c r="F51" s="7"/>
-      <c r="G51" s="7"/>
-      <c r="H51" s="5"/>
-      <c r="I51" s="5"/>
+      <c r="F51" s="12">
+        <v>195480</v>
+      </c>
+      <c r="G51" s="12"/>
+      <c r="H51" s="6"/>
+      <c r="I51" s="6"/>
       <c r="K51" s="3">
         <f>(F51+H51)*3%</f>
-        <v>0</v>
+        <v>5864.4</v>
       </c>
     </row>
     <row r="54" spans="5:11" x14ac:dyDescent="0.3">
@@ -895,26 +897,26 @@
       <c r="E55" t="s">
         <v>6</v>
       </c>
-      <c r="H55" s="5" t="s">
+      <c r="H55" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="I55" s="5"/>
-      <c r="J55" s="5"/>
-      <c r="K55" s="5"/>
+      <c r="I55" s="6"/>
+      <c r="J55" s="6"/>
+      <c r="K55" s="6"/>
     </row>
     <row r="56" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="E56" s="8">
+      <c r="E56" s="5">
         <f>F7+H7+H11+F11+F15+H15+H19+F19+F23+H23+H27+F27+F31+H35+F35+H32+H31+H39+F39+F43+H43+H47+F47+F51+H51</f>
-        <v>956197.81</v>
-      </c>
-      <c r="F56" s="8"/>
-      <c r="G56" s="8"/>
-      <c r="H56" s="8">
+        <v>1151677.81</v>
+      </c>
+      <c r="F56" s="5"/>
+      <c r="G56" s="5"/>
+      <c r="H56" s="5">
         <f>SUM(K7:K51)</f>
-        <v>28685.934300000001</v>
-      </c>
-      <c r="I56" s="9"/>
-      <c r="J56" s="9"/>
+        <v>34550.334300000002</v>
+      </c>
+      <c r="I56" s="7"/>
+      <c r="J56" s="7"/>
     </row>
     <row r="58" spans="5:11" x14ac:dyDescent="0.3">
       <c r="G58" s="4" t="s">
@@ -922,15 +924,52 @@
       </c>
     </row>
     <row r="59" spans="5:11" x14ac:dyDescent="0.3">
-      <c r="G59" s="10">
+      <c r="G59" s="8">
         <f>E56+H56</f>
-        <v>984883.74430000002</v>
-      </c>
-      <c r="H59" s="10"/>
-      <c r="I59" s="10"/>
+        <v>1186228.1443</v>
+      </c>
+      <c r="H59" s="8"/>
+      <c r="I59" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="53">
+    <mergeCell ref="H51:I51"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="H43:I43"/>
+    <mergeCell ref="H46:I46"/>
+    <mergeCell ref="H47:I47"/>
+    <mergeCell ref="H50:I50"/>
+    <mergeCell ref="H30:I30"/>
+    <mergeCell ref="H31:I31"/>
+    <mergeCell ref="H34:I34"/>
+    <mergeCell ref="H35:I35"/>
+    <mergeCell ref="H38:I38"/>
+    <mergeCell ref="H19:I19"/>
+    <mergeCell ref="H22:I22"/>
+    <mergeCell ref="H23:I23"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="H27:I27"/>
+    <mergeCell ref="F47:G47"/>
+    <mergeCell ref="F51:G51"/>
+    <mergeCell ref="H6:I6"/>
+    <mergeCell ref="H7:I7"/>
+    <mergeCell ref="H10:I10"/>
+    <mergeCell ref="H11:I11"/>
+    <mergeCell ref="H14:I14"/>
+    <mergeCell ref="H15:I15"/>
+    <mergeCell ref="H18:I18"/>
+    <mergeCell ref="F46:G46"/>
+    <mergeCell ref="F50:G50"/>
+    <mergeCell ref="F7:G7"/>
+    <mergeCell ref="F11:G11"/>
+    <mergeCell ref="F15:G15"/>
+    <mergeCell ref="F19:G19"/>
+    <mergeCell ref="H42:I42"/>
+    <mergeCell ref="F22:G22"/>
+    <mergeCell ref="F26:G26"/>
+    <mergeCell ref="F30:G30"/>
+    <mergeCell ref="F34:G34"/>
+    <mergeCell ref="F43:G43"/>
     <mergeCell ref="E56:G56"/>
     <mergeCell ref="H55:K55"/>
     <mergeCell ref="H56:J56"/>
@@ -947,43 +986,6 @@
     <mergeCell ref="F27:G27"/>
     <mergeCell ref="F31:G31"/>
     <mergeCell ref="F35:G35"/>
-    <mergeCell ref="F22:G22"/>
-    <mergeCell ref="F26:G26"/>
-    <mergeCell ref="F30:G30"/>
-    <mergeCell ref="F34:G34"/>
-    <mergeCell ref="F43:G43"/>
-    <mergeCell ref="F47:G47"/>
-    <mergeCell ref="F51:G51"/>
-    <mergeCell ref="H6:I6"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="H10:I10"/>
-    <mergeCell ref="H11:I11"/>
-    <mergeCell ref="H14:I14"/>
-    <mergeCell ref="H15:I15"/>
-    <mergeCell ref="H18:I18"/>
-    <mergeCell ref="F46:G46"/>
-    <mergeCell ref="F50:G50"/>
-    <mergeCell ref="F7:G7"/>
-    <mergeCell ref="F11:G11"/>
-    <mergeCell ref="F15:G15"/>
-    <mergeCell ref="F19:G19"/>
-    <mergeCell ref="H42:I42"/>
-    <mergeCell ref="H19:I19"/>
-    <mergeCell ref="H22:I22"/>
-    <mergeCell ref="H23:I23"/>
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="H27:I27"/>
-    <mergeCell ref="H30:I30"/>
-    <mergeCell ref="H31:I31"/>
-    <mergeCell ref="H34:I34"/>
-    <mergeCell ref="H35:I35"/>
-    <mergeCell ref="H38:I38"/>
-    <mergeCell ref="H51:I51"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="H43:I43"/>
-    <mergeCell ref="H46:I46"/>
-    <mergeCell ref="H47:I47"/>
-    <mergeCell ref="H50:I50"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
